--- a/运气工程/运气工程-00-系列索引.xlsx
+++ b/运气工程/运气工程-00-系列索引.xlsx
@@ -1068,5 +1068,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:J43" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>